--- a/data/questions.xlsx
+++ b/data/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="8_{0BB893E9-6CFF-4A63-B5D9-D904D6B46875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADAFA167-BC02-49CA-8FCC-F01ABD38EFCF}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="8_{0BB893E9-6CFF-4A63-B5D9-D904D6B46875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F015B0-76A3-4C3B-AC71-A5E31E2BE8EA}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="1425" windowWidth="15450" windowHeight="11625" xr2:uid="{9083BA9B-6AB7-4B5E-A0ED-E23B70A39331}"/>
+    <workbookView xWindow="11715" yWindow="2910" windowWidth="15450" windowHeight="11490" xr2:uid="{9083BA9B-6AB7-4B5E-A0ED-E23B70A39331}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,14 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>「あ」から始まるキャラ</t>
   </si>
   <si>
-    <t>技名に「拳」と入る技</t>
-  </si>
-  <si>
     <t>ルフィの技（ゴムゴムのは省略可）</t>
   </si>
   <si>
@@ -121,9 +118,6 @@
   </si>
   <si>
     <t>白ひげ海賊団傘下のキャラ</t>
-  </si>
-  <si>
-    <t>ロジャー海賊団のメンバー</t>
   </si>
   <si>
     <t>キッド海賊団のメンバー</t>
@@ -205,17 +199,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>「さ行」から始まる技</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>「た行」から始まる技</t>
-    <rPh sb="2" eb="3">
-      <t>ギョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>「な行」から始まる技</t>
     <rPh sb="2" eb="3">
       <t>ギョウ</t>
@@ -244,13 +227,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>「ら行」から始まる技</t>
-    <rPh sb="2" eb="3">
-      <t>ギョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>“アラバスタ編”で初登場するエクストラキャラ　12巻～23巻</t>
     <rPh sb="25" eb="26">
       <t>カン</t>
@@ -749,6 +725,193 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「ら行」から始まる技（嵐脚は除く）</t>
+    <rPh sb="2" eb="3">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ランキャク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「さ行」から始まる技（指銃は除く）</t>
+    <rPh sb="11" eb="12">
+      <t>ユビ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ジュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「た行」から始まる技（鉄塊は除く）</t>
+    <rPh sb="2" eb="3">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テッカイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「拳」と入る技</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「火」と入る技</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ギフターズの名前（飛び六胞・真打ちは除く）</t>
+    <rPh sb="6" eb="8">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ロク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シンウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>真打ちの名前（飛び六胞は除く）</t>
+    <rPh sb="0" eb="2">
+      <t>シンウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ロク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ロジャー海賊団のメンバー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>電伝虫を使った描写のあるキャラ（麦わらの一味を除く）</t>
+    <rPh sb="0" eb="3">
+      <t>デンデンムシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ビョウシャ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ムギ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イチミ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サブタイトル○○の冒険</t>
+    <rPh sb="9" eb="11">
+      <t>ボウケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メリー号に乗った事のあるキャラ（麦わらの一味を除く）</t>
+    <rPh sb="3" eb="4">
+      <t>ゴウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ムギ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イチミ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>肩書きで副○○と書かれた事のあるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>カタガ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>コト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ワンピースにしか登場しない動物の種族名</t>
+    <rPh sb="8" eb="10">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ドウブツ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>シュゾクメイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -825,6 +988,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1124,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6C76D14-6B6D-4641-9D9E-9292262CE35A}">
-  <dimension ref="A1:A109"/>
+  <dimension ref="A1:A117"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="107" customWidth="1"/>
@@ -1137,542 +1304,582 @@
     </row>
     <row r="2" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>1</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>2</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>71</v>
+      <c r="A35" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="1" t="s">
-        <v>3</v>
+      <c r="A36" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>76</v>
+      <c r="A41" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="1" t="s">
-        <v>87</v>
+      <c r="A54" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
-        <v>92</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="1" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="1" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
     </row>
     <row r="101" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="108" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="109" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/data/questions.xlsx
+++ b/data/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="8_{0BB893E9-6CFF-4A63-B5D9-D904D6B46875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F015B0-76A3-4C3B-AC71-A5E31E2BE8EA}"/>
+  <xr:revisionPtr revIDLastSave="368" documentId="8_{0BB893E9-6CFF-4A63-B5D9-D904D6B46875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFC02475-24C0-4FAF-989A-9DF2F4087839}"/>
   <bookViews>
-    <workbookView xWindow="11715" yWindow="2910" windowWidth="15450" windowHeight="11490" xr2:uid="{9083BA9B-6AB7-4B5E-A0ED-E23B70A39331}"/>
+    <workbookView xWindow="10635" yWindow="4875" windowWidth="9480" windowHeight="10275" xr2:uid="{9083BA9B-6AB7-4B5E-A0ED-E23B70A39331}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
   <si>
     <t>「あ」から始まるキャラ</t>
   </si>
@@ -111,12 +111,6 @@
     <t>好物にフルーツ名が入るキャラ</t>
   </si>
   <si>
-    <t>懸賞金5000万以下のキャラ</t>
-  </si>
-  <si>
-    <t>懸賞金5000万以上、1億以下のキャラ（一度でも範囲内の懸賞金額をかけられた事があれば）</t>
-  </si>
-  <si>
     <t>白ひげ海賊団傘下のキャラ</t>
   </si>
   <si>
@@ -166,22 +160,6 @@
   </si>
   <si>
     <t>「お」から始まるキャラ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>「か」から始まるキャラ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>「き」から始まるキャラ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>「く」から始まるキャラ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>「こ」から始まるキャラ</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -768,10 +746,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>技名に「拳」と入る技</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>技名に「火」と入る技</t>
     <rPh sb="0" eb="2">
       <t>ワザメイ</t>
@@ -912,6 +886,1589 @@
     </rPh>
     <rPh sb="16" eb="19">
       <t>シュゾクメイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「か」から始まるキャラ　濁点あり</t>
+    <rPh sb="12" eb="14">
+      <t>ダクテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「き」から始まるキャラ　濁点あり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「く」から始まるキャラ　濁点あり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「こ」から始まるキャラ　濁点あり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「さ」から始まるキャラ　濁点あり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「し」から始まるキャラ※シャーロット家を除く　濁点あり</t>
+    <rPh sb="18" eb="19">
+      <t>イエ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「す」から始まるキャラ　濁点あり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「せ」から始まるキャラ　濁点あり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「そ」から始まるキャラ　濁点あり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「け」から始まるキャラ　濁点あり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「た」から始まるキャラ　濁点あり</t>
+    <rPh sb="12" eb="14">
+      <t>ダクテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「ち」から始まるキャラ　濁点あり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「て」から始まるキャラ　濁点あり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「と」から始まるキャラ　濁点あり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「な」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「に」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「ね」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「の」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「は」から始まるキャラ　濁点半濁点あり</t>
+    <rPh sb="12" eb="14">
+      <t>ダクテン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ハンダクテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「ひ」から始まるキャラ　濁点半濁点あり</t>
+    <rPh sb="12" eb="14">
+      <t>ダクテン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ハンダクテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「ふ」から始まるキャラ　濁点半濁点あり</t>
+    <rPh sb="12" eb="14">
+      <t>ダクテン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ハンダクテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「へ」から始まるキャラ　濁点半濁点あり</t>
+    <rPh sb="12" eb="14">
+      <t>ダクテン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ハンダクテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「ほ」から始まるキャラ　濁点半濁点あり</t>
+    <rPh sb="12" eb="14">
+      <t>ダクテン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ハンダクテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「ま」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「み」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「む」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「め」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「も」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「や」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「ゆ」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「よ」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「ら」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「り」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「る」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「れ」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「ろ」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「わ」から始まるキャラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>名前がひらがなのみのキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>懸賞金5000万以上、1億未満のキャラ（一度でも範囲内の懸賞金額をかけられた事があれば）</t>
+    <rPh sb="13" eb="15">
+      <t>ミマン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>懸賞金5000万未満のキャラ</t>
+    <rPh sb="8" eb="10">
+      <t>ミマン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>懸賞金1億以上、2億未満のキャラ（一度でも範囲内の懸賞金額をかけられた事があれば）</t>
+    <rPh sb="4" eb="5">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ミマン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>懸賞金2億以上、3億未満のキャラ（一度でも範囲内の懸賞金額をかけられた事があれば）</t>
+    <rPh sb="4" eb="5">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ミマン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>懸賞金3億以上、5億未満のキャラ（一度でも範囲内の懸賞金額をかけられた事があれば）</t>
+    <rPh sb="4" eb="5">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ミマン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>世界会議参加国を除き、麦わらの一味が誰も訪れた事のない島or国の名前を答えよ</t>
+    <rPh sb="0" eb="4">
+      <t>セカイカイギ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サンカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>クニ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ムギ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチミ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オトズ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シマ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>クニ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海軍中将と戦った事のあるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>カイグン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チュウジョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タタカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>コト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>七武海と戦った描写のあるキャラ（麦わらの一味を除く）</t>
+    <rPh sb="0" eb="3">
+      <t>シチブカイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タタカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ビョウシャ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ムギ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イチミ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>享年が明らかになっているキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>キョウネン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SBSに描かれた事のあるキャラ（文字ではなく絵として）</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>扉絵でしか登場した事のないキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>トビラエ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>作中で登場する料理名or食べ物名（現実世界にあるものは除く）</t>
+    <rPh sb="0" eb="2">
+      <t>サクチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>リョウリメイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゲンジツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>色が入る異名</t>
+    <rPh sb="0" eb="1">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イミョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ギア4で使われた事のある技（ゴムゴムのは省略可）</t>
+    <rPh sb="4" eb="5">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>ショウリャクカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「拳」と入る技（○○拳法は除く）</t>
+    <rPh sb="13" eb="15">
+      <t>ケンポウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「風」が付く技</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「神」が付く技</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「漢数字」が入る技（ロビンの技、魚人空手、〇刀流は除く）</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>カンスウジ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>ギョジンカラテ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カタナ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「星」が入る技（ウソップの技は除く）</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「爆」が付く技</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>バク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「斬」が付く技（ゾロとダズの技は除く）</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ザン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「海」が付く技</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「空」が付く技</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ソラ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「色の名前」が付く技</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「曜日の名前」が入る技</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨウビ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「王」が付く技</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「撃」が付く技</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>技名に「砲」が付く技</t>
+    <rPh sb="0" eb="2">
+      <t>ワザメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「男」が含まれるサブタイトル</t>
+    <rPh sb="1" eb="2">
+      <t>オトコ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「女」が含まれるサブタイトル</t>
+    <rPh sb="1" eb="2">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「国」が含まれるサブタイトル</t>
+    <rPh sb="1" eb="2">
+      <t>クニ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「夢」が含まれるサブタイトル</t>
+    <rPh sb="1" eb="2">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「神」が含まれるサブタイトル</t>
+    <rPh sb="1" eb="2">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「王」が含まれるサブタイトル</t>
+    <rPh sb="1" eb="2">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「漢数字」が含まれるサブタイトル（一は除く）</t>
+    <rPh sb="1" eb="4">
+      <t>カンスウジ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「○○と○○」というサブタイトル　例.海賊王と大剣豪</t>
+    <rPh sb="17" eb="18">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>カイゾクオウ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ダイケンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「○○登場」というサブタイトル</t>
+    <rPh sb="3" eb="5">
+      <t>トウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「色の名前」が含まれるサブタイトル</t>
+    <rPh sb="1" eb="2">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「月」が含まれるサブタイトル</t>
+    <rPh sb="1" eb="2">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「上」が含まれるサブタイトル</t>
+    <rPh sb="1" eb="2">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「！」が含まれるサブタイトル</t>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「、」が含まれるサブタイトル</t>
+    <rPh sb="4" eb="5">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キャラクターの名前にアルファベットが使われているキャラ</t>
+    <rPh sb="7" eb="9">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好物がリンゴ関連のキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好物がバナナ関係のキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好物に「高」という文字が含まれるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウ)</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好物に「肉」という文字が含まれるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ニク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好物に「酒」という文字が含まれるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サケ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好物が麺類のキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>メンルイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好物がカタカナのみで構成されているキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>名前に「ー」が2回以上使われるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>カイイジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>名前に「ん」が2回以上使われるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>カイイジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>名前に「っ」が含まれるキャラ※表記は問わない</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>名前に濁点と半濁点両方が含まれるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ダクテン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ハンダクテン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>リョウホウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>作中で「非能力者時代」と「能力者時代」が描かれているキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>サクチュウ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ヒノウリョクシャ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジダイ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ノウリョクシャ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジダイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好物が野菜類のキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ヤサイルイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好物に「魚」が含まれるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好物に「キャラクター名」が含まれるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キャラ名+そのキャラの趣味</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キャラ名+そのキャラの嫌いな食べ物</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キラ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キャラ名+そのキャラの好きな季節</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キセツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キャラ名+そのキャラの好きな季</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>船の名前</t>
+    <rPh sb="0" eb="1">
+      <t>フネ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海賊船以外の乗り物の名前</t>
+    <rPh sb="0" eb="3">
+      <t>カイゾクセン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ジャヤの森で登場した生き物</t>
+    <rPh sb="4" eb="5">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>両親の名前が判明しているキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>リョウシン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンメイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アプーの全身にある楽器の名前</t>
+    <rPh sb="4" eb="6">
+      <t>ゼンシン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガッキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルフィが名前で呼んだ事のあるキャラ（一味以外）</t>
+    <rPh sb="4" eb="6">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イチミ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イガイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>本名以外に別名があるキャラ（バロックワークスのコードネームは除く）</t>
+    <rPh sb="0" eb="2">
+      <t>ホンミョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ベツメイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>東の海出身ではないが東の海にいる描写のあるキャラ</t>
+    <rPh sb="0" eb="1">
+      <t>ヒガシ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ウミシュッシン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヒガシ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ビョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルフィの手配書を持つ描写のあるキャラ</t>
+    <rPh sb="4" eb="7">
+      <t>テハイショ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ビョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>麦わらの一味2名と戦った事のあるキャラ　※3名以上は含まない</t>
+    <rPh sb="0" eb="1">
+      <t>ムギ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イチミ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タタカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>作中で自身の懸賞金額を口にした事のあるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>サクチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ケンショウキンガク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>クチ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>コト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>雪が降る描写のある場所</t>
+    <rPh sb="0" eb="1">
+      <t>ユキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ビョウシャ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>妖刀に触れた事のあるキャラ</t>
+    <rPh sb="0" eb="1">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>カタナ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自身の異名を口にした事があるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イミョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>クチ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鼻をほじる描写のあるキャラ</t>
+    <rPh sb="0" eb="1">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ビョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ウインクした事のあるキャラ</t>
+    <rPh sb="6" eb="7">
+      <t>コト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>泡を吹く描写のあるキャラ</t>
+    <rPh sb="0" eb="1">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ビョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>骨付き肉を食べる描写のあるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>ホネツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ビョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鞭を使うキャラ</t>
+    <rPh sb="0" eb="1">
+      <t>ムチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>斧を使うキャラ</t>
+    <rPh sb="0" eb="1">
+      <t>オノ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ハンマーを使うキャラ</t>
+    <rPh sb="5" eb="6">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>弓を使うキャラ（女ヶ島出身のキャラを除く）</t>
+    <rPh sb="0" eb="1">
+      <t>ユミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ニョウガシマ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュッシン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>羽ペンを持つ描写のあるキャラ</t>
+    <rPh sb="0" eb="1">
+      <t>ハネ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ビョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョッパーが翻訳した事のある動物</t>
+    <rPh sb="6" eb="8">
+      <t>ホンヤク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ドウブツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マイクを持つ描写のあるキャラ</t>
+    <rPh sb="4" eb="5">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ビョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>傘を持つ描写のあるキャラ</t>
+    <rPh sb="0" eb="1">
+      <t>カサ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ビョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>楽器を使う描写のあるキャラ</t>
+    <rPh sb="0" eb="2">
+      <t>ガッキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ビョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マッチ棒を使う描写のあるキャラ</t>
+    <rPh sb="3" eb="4">
+      <t>ボウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ビョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>話の最後のコマに肩書きを描かれた事のあるキャラ</t>
+    <rPh sb="0" eb="1">
+      <t>ハナシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カタガ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>コト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エースのTシャツに書かれた事のある言葉</t>
+    <rPh sb="9" eb="10">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コトバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルフィがゴムゴムの銃を使った事のある相手</t>
+    <rPh sb="9" eb="10">
+      <t>ジュウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>アイテ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゾロが鬼斬りを使った事のある相手</t>
+    <rPh sb="3" eb="5">
+      <t>オニギ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>アイテ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海列車で使われた技</t>
+    <rPh sb="0" eb="3">
+      <t>ウミレッシャ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>表紙に動物が描かれている巻　巻数+動物名</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウシ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ドウブツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>ドウブツメイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1291,7 +2848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6C76D14-6B6D-4641-9D9E-9292262CE35A}">
-  <dimension ref="A1:A117"/>
+  <dimension ref="A1:A244"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="107" customWidth="1"/>
@@ -1304,582 +2861,1217 @@
     </row>
     <row r="2" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>1</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>61</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
-        <v>65</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>66</v>
+      <c r="A36" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>2</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>3</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>4</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>73</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" t="s">
-        <v>71</v>
+      <c r="A42" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>70</v>
+      <c r="A43" s="1" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" t="s">
-        <v>67</v>
+      <c r="A44" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
-        <v>68</v>
+      <c r="A45" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
-        <v>69</v>
+      <c r="A46" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" t="s">
-        <v>74</v>
+      <c r="A47" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" t="s">
-        <v>75</v>
+      <c r="A48" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" t="s">
-        <v>76</v>
+      <c r="A49" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
-        <v>77</v>
+      <c r="A50" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
-        <v>78</v>
+      <c r="A51" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
-        <v>79</v>
+      <c r="A52" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" t="s">
-        <v>80</v>
+      <c r="A53" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
-        <v>81</v>
+      <c r="A54" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
-        <v>96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="1" t="s">
-        <v>85</v>
+      <c r="A70" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="1" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="1" t="s">
-        <v>90</v>
+      <c r="A77" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="1" t="s">
-        <v>91</v>
+      <c r="A78" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="1" t="s">
-        <v>92</v>
+      <c r="A79" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="1" t="s">
-        <v>8</v>
+      <c r="A80" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="1" t="s">
-        <v>9</v>
+      <c r="A81" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="1" t="s">
-        <v>10</v>
+      <c r="A82" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="1" t="s">
-        <v>11</v>
+      <c r="A83" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="84" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="1" t="s">
-        <v>12</v>
+      <c r="A84" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="1" t="s">
-        <v>13</v>
+      <c r="A85" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="1" t="s">
-        <v>14</v>
+      <c r="A86" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="87" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="1" t="s">
-        <v>15</v>
+      <c r="A87" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="1" t="s">
-        <v>16</v>
+      <c r="A88" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="1" t="s">
-        <v>17</v>
+      <c r="A89" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="90" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="1" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="1" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="1" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="1" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="1" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="1" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="1" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="98" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="1" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="1" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
     </row>
     <row r="100" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="1" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="1" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
     </row>
     <row r="102" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="1" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
     </row>
     <row r="103" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="1" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="1" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
     </row>
     <row r="105" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="1" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="1" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="1" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
     </row>
     <row r="110" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A111" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A112" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A115" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A118" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A119" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A120" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A123" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A125" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A126" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A128" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A129" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A130" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A133" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A139" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A140" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A146" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A147" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A148" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A149" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A150" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A151" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A152" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A153" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A154" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A155" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A112" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A113" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A114" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A115" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A116" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A117" t="s">
-        <v>116</v>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A156" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A157" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A158" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A159" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A160" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A161" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A162" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A164" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A165" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A166" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A167" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A168" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A169" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A170" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A171" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A172" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A173" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A174" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A175" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A176" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A177" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A178" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A179" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A180" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A181" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A182" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A183" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A184" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A185" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A186" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A187" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A188" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A189" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A190" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A191" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A192" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A193" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A194" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A195" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A196" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A197" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A198" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A199" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A200" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A201" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A202" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A203" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A204" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A205" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A206" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A207" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A208" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A209" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A210" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A211" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A212" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A213" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A214" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A215" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A216" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A217" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A218" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A219" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A220" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A221" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A222" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A223" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A224" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A225" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A226" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A227" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A228" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A229" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A230" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A231" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A232" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A233" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A234" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A235" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A236" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A237" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A238" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A239" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A240" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A241" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A242" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A243" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A244" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/data/questions.xlsx
+++ b/data/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="368" documentId="8_{0BB893E9-6CFF-4A63-B5D9-D904D6B46875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFC02475-24C0-4FAF-989A-9DF2F4087839}"/>
+  <xr:revisionPtr revIDLastSave="371" documentId="8_{0BB893E9-6CFF-4A63-B5D9-D904D6B46875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4687336F-C357-4458-87B8-AA30848E0EFF}"/>
   <bookViews>
-    <workbookView xWindow="10635" yWindow="4875" windowWidth="9480" windowHeight="10275" xr2:uid="{9083BA9B-6AB7-4B5E-A0ED-E23B70A39331}"/>
+    <workbookView xWindow="13800" yWindow="7470" windowWidth="15450" windowHeight="8460" xr2:uid="{9083BA9B-6AB7-4B5E-A0ED-E23B70A39331}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <si>
     <t>「あ」から始まるキャラ</t>
   </si>
@@ -2469,6 +2469,42 @@
     </rPh>
     <rPh sb="17" eb="20">
       <t>ドウブツメイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>天竜人の○○家</t>
+    <rPh sb="0" eb="3">
+      <t>テンリュウビト</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>イエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>種族の名前</t>
+    <rPh sb="0" eb="2">
+      <t>シュゾク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>作中に登場した病気の名前</t>
+    <rPh sb="0" eb="2">
+      <t>サクチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ビョウキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ナマエ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2848,7 +2884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6C76D14-6B6D-4641-9D9E-9292262CE35A}">
-  <dimension ref="A1:A244"/>
+  <dimension ref="A1:A247"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="107" customWidth="1"/>
@@ -4074,6 +4110,21 @@
         <v>243</v>
       </c>
     </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A245" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A246" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A247" t="s">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/questions.xlsx
+++ b/data/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="371" documentId="8_{0BB893E9-6CFF-4A63-B5D9-D904D6B46875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4687336F-C357-4458-87B8-AA30848E0EFF}"/>
+  <xr:revisionPtr revIDLastSave="411" documentId="8_{0BB893E9-6CFF-4A63-B5D9-D904D6B46875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83BFDEB2-7E42-4E5E-BDC3-203965BF28F1}"/>
   <bookViews>
-    <workbookView xWindow="13800" yWindow="7470" windowWidth="15450" windowHeight="8460" xr2:uid="{9083BA9B-6AB7-4B5E-A0ED-E23B70A39331}"/>
+    <workbookView xWindow="765" yWindow="6375" windowWidth="13005" windowHeight="8745" xr2:uid="{9083BA9B-6AB7-4B5E-A0ED-E23B70A39331}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,20 +34,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
   <si>
     <t>「あ」から始まるキャラ</t>
   </si>
   <si>
-    <t>ルフィの技（ゴムゴムのは省略可）</t>
-  </si>
-  <si>
     <t>ギア2で使われた事のある技（ゴムゴムのJETは省略可）</t>
   </si>
   <si>
-    <t>「ルフィ」と「vs.」が入るサブタイトル（vs.の表記は問わない）</t>
-  </si>
-  <si>
     <t>「vs.」が入り、「ルフィ」が入らないサブタイトル（vs.の表記は問わない）</t>
   </si>
   <si>
@@ -70,12 +64,6 @@
   </si>
   <si>
     <t>北の海出身のキャラ</t>
-  </si>
-  <si>
-    <t>ビッグマムの息子の名前</t>
-  </si>
-  <si>
-    <t>ビッグマムも娘の名前</t>
   </si>
   <si>
     <t>息子or娘の名前が判明しているキャラ</t>
@@ -271,81 +259,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ゾロの技（○○刀流は省略可）</t>
-    <rPh sb="3" eb="4">
-      <t>ワザ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>カタナ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>リュウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ショウリャク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>サンジの技</t>
-    <rPh sb="4" eb="5">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ナミの技</t>
-    <rPh sb="3" eb="4">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ウソップの技</t>
-    <rPh sb="5" eb="6">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ロビンの技</t>
-    <rPh sb="4" eb="5">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>チョッパーの技</t>
-    <rPh sb="6" eb="7">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>フランキーの技</t>
-    <rPh sb="6" eb="7">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ブルックの技</t>
-    <rPh sb="5" eb="6">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ジンベエの技</t>
-    <rPh sb="5" eb="6">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>指銃の派生技</t>
     <rPh sb="0" eb="1">
       <t>ユビ</t>
@@ -2506,6 +2419,223 @@
     <rPh sb="10" eb="12">
       <t>ナマエ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年前のギアを使わないルフィの技（ゴムゴムのは省略）</t>
+    <rPh sb="1" eb="3">
+      <t>ネンマエ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年前のゾロの技（○○刀流は省略）</t>
+    <rPh sb="1" eb="3">
+      <t>ネンマエ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カタナ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショウリャク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年前のサンジの技（連携技は禁止　連携技は最後のもののみ）</t>
+    <rPh sb="8" eb="9">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キンシ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>レンケイワザ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サイゴ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年前のナミの技</t>
+    <rPh sb="7" eb="8">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年前のウソップの技</t>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年前のロビンの技</t>
+    <rPh sb="8" eb="9">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年前のチョッパーの技</t>
+    <rPh sb="10" eb="11">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年前のフランキーの技</t>
+    <rPh sb="10" eb="11">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年前のブルックの技</t>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年後のルフィの技（ゴムゴムのは省略）（2年前初登場のものは禁止）</t>
+    <rPh sb="21" eb="23">
+      <t>ネンマエ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ハツトウジョウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>キンシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年後のゾロの技（○○刀流は省略）（2年前初登場のものは禁止）</t>
+    <rPh sb="7" eb="8">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カタナ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショウリャク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年後のサンジの技（連携技は禁止　連携技は最後のもののみ）（2年前初登場のものは禁止）</t>
+    <rPh sb="8" eb="9">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キンシ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>レンケイワザ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サイゴ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年後のナミの技（2年前初登場のものは禁止）</t>
+    <rPh sb="7" eb="8">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年後のウソップの技（2年前初登場のものは禁止）</t>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年後のロビンの技（2年前初登場のものは禁止）</t>
+    <rPh sb="8" eb="9">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年後のチョッパーの技（2年前初登場のものは禁止）</t>
+    <rPh sb="10" eb="11">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年後のフランキーの技（フランキー将軍は除く）（2年前初登場のものは禁止）</t>
+    <rPh sb="10" eb="11">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショウグン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2年後のブルックの技（2年前初登場のものは禁止）</t>
+    <rPh sb="9" eb="10">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ジンベエの技（魚人空手省略可）</t>
+    <rPh sb="5" eb="6">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ギョジンカラテ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ショウリャクカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「ルフィ」と「vs.」が入るサブタイトル（vs.の表記は問わない）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ビッグ・マムの息子の名前</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ビッグ・マムも娘の名前</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2884,7 +3014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6C76D14-6B6D-4641-9D9E-9292262CE35A}">
-  <dimension ref="A1:A247"/>
+  <dimension ref="A1:A256"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="107" customWidth="1"/>
@@ -2897,537 +3027,537 @@
     </row>
     <row r="2" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
-        <v>1</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
-        <v>52</v>
+        <v>235</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
-        <v>53</v>
+        <v>236</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
-        <v>54</v>
+        <v>237</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
-        <v>56</v>
+        <v>239</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
-        <v>57</v>
+        <v>240</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
-        <v>58</v>
+        <v>241</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
-        <v>59</v>
+        <v>242</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" t="s">
-        <v>60</v>
+      <c r="A70" s="1" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
-        <v>2</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
-        <v>161</v>
+        <v>245</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="1" t="s">
-        <v>4</v>
+        <v>247</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
-        <v>67</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
-        <v>66</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" t="s">
-        <v>65</v>
+      <c r="A77" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" t="s">
-        <v>64</v>
+      <c r="A78" s="1" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>61</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" t="s">
-        <v>62</v>
+      <c r="A80" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" t="s">
-        <v>63</v>
+      <c r="A81" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" t="s">
-        <v>68</v>
+      <c r="A82" s="1" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" t="s">
-        <v>69</v>
+      <c r="A83" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" t="s">
-        <v>70</v>
+      <c r="A84" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" t="s">
-        <v>71</v>
+      <c r="A85" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="87" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="1" t="s">
-        <v>76</v>
+      <c r="A90" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="1" t="s">
-        <v>77</v>
+      <c r="A91" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="1" t="s">
-        <v>5</v>
+      <c r="A92" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="93" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="1" t="s">
-        <v>87</v>
+      <c r="A93" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="1" t="s">
-        <v>88</v>
+      <c r="A94" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="1" t="s">
-        <v>89</v>
+      <c r="A95" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="1" t="s">
-        <v>90</v>
+      <c r="A96" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="1" t="s">
-        <v>91</v>
+      <c r="A97" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="98" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="1" t="s">
-        <v>92</v>
+      <c r="A98" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="99" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="1" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
     </row>
     <row r="100" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="1" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="1" t="s">
-        <v>95</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="1" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
     </row>
     <row r="103" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="1" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="105" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="106" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="107" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
     </row>
     <row r="108" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="109" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3452,677 +3582,722 @@
     </row>
     <row r="113" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="114" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="1" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="115" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="1" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
     </row>
     <row r="116" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="1" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
     </row>
     <row r="119" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="1" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="120" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="1" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="1" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
     </row>
     <row r="122" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="1" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="123" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="1" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
     </row>
     <row r="124" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="1" t="s">
-        <v>21</v>
+        <v>254</v>
       </c>
     </row>
     <row r="129" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="1" t="s">
-        <v>22</v>
+        <v>255</v>
       </c>
     </row>
     <row r="130" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="1" t="s">
-        <v>149</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="1" t="s">
-        <v>148</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="1" t="s">
-        <v>150</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="1" t="s">
-        <v>151</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="1" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="138" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="1" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="1" t="s">
-        <v>28</v>
+        <v>136</v>
       </c>
     </row>
     <row r="142" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="1" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
     </row>
     <row r="143" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="1" t="s">
-        <v>30</v>
+        <v>137</v>
       </c>
     </row>
     <row r="144" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="1" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
     </row>
     <row r="145" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="1" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
     </row>
     <row r="146" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="1" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="148" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A149" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A150" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A151" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A152" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A153" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A154" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A155" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A156" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A157" t="s">
-        <v>154</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A149" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A150" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A151" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A152" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A153" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A154" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A155" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A156" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A157" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>156</v>
+        <v>90</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>157</v>
+        <v>92</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>158</v>
+        <v>93</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>246</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A248" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A249" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A250" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A251" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A252" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A253" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A254" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A255" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A256" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
